--- a/server/master-excel-files/Central_BIOLOGY_Grade 10.xlsx
+++ b/server/master-excel-files/Central_BIOLOGY_Grade 10.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\BIOLOGY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,9 +30,6 @@
     <t>JUNE</t>
   </si>
   <si>
-    <t>Not Started</t>
-  </si>
-  <si>
     <t>JULY</t>
   </si>
   <si>
@@ -127,6 +124,9 @@
   </si>
   <si>
     <t>4. Reproductive health</t>
+  </si>
+  <si>
+    <t>Not Assigned</t>
   </si>
 </sst>
 </file>
@@ -168,7 +168,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -261,24 +261,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -286,14 +273,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -307,17 +297,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,570 +609,559 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="38.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="13" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="7"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="8"/>
     </row>
     <row r="3" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>31</v>
+        <v>19</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="H1:H2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="I1:I2"/>
@@ -1198,10 +1171,18 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 C1:I1 C3:I13 K3:N13">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="K1:N1 C1:I1">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="C3:I13 K3:N13">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
